--- a/transit.xlsx
+++ b/transit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dipty\ipynb\Scaler\Scaler_ML_self\Curr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{362CE655-6D6B-452F-8443-FFC708D0F171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1C5A7F9-7B5D-4441-9718-CC91144829C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,10 +269,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -630,6 +626,18 @@
       <c r="F3">
         <v>250</v>
       </c>
+      <c r="G3">
+        <v>200</v>
+      </c>
+      <c r="H3">
+        <v>500</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
       <c r="K3">
         <f>K2+1</f>
         <v>1034</v>
@@ -654,6 +662,18 @@
       <c r="F4">
         <v>250</v>
       </c>
+      <c r="G4">
+        <v>200</v>
+      </c>
+      <c r="H4">
+        <v>500</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
       <c r="K4">
         <f t="shared" ref="K4:K30" si="0">K3+1</f>
         <v>1035</v>
@@ -676,7 +696,19 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>250</v>
+        <v>1100</v>
+      </c>
+      <c r="G5">
+        <v>200</v>
+      </c>
+      <c r="H5">
+        <v>500</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
@@ -772,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>

--- a/transit.xlsx
+++ b/transit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dipty\ipynb\Scaler\Scaler_ML_self\Curr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1C5A7F9-7B5D-4441-9718-CC91144829C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5C860FA-8B65-475D-9B56-86499485B0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -269,6 +269,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -734,6 +738,18 @@
       <c r="F6">
         <v>250</v>
       </c>
+      <c r="G6">
+        <v>200</v>
+      </c>
+      <c r="H6">
+        <v>500</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
       <c r="K6">
         <f t="shared" si="0"/>
         <v>1037</v>
@@ -758,6 +774,18 @@
       <c r="F7">
         <v>250</v>
       </c>
+      <c r="G7">
+        <v>200</v>
+      </c>
+      <c r="H7">
+        <v>500</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
       <c r="K7">
         <f t="shared" si="0"/>
         <v>1038</v>
@@ -782,6 +810,18 @@
       <c r="F8">
         <v>530</v>
       </c>
+      <c r="G8">
+        <v>200</v>
+      </c>
+      <c r="H8">
+        <v>500</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
       <c r="K8">
         <f t="shared" si="0"/>
         <v>1039</v>
@@ -805,6 +845,18 @@
       </c>
       <c r="F9">
         <v>390</v>
+      </c>
+      <c r="G9">
+        <v>200</v>
+      </c>
+      <c r="H9">
+        <v>500</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
